--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27F73182-36F6-4757-AEC4-22E870A98F45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6B4128-7D74-4EC5-81D5-CFF20E5DB199}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9948E6B1-4C09-41B0-9020-903819E59839}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F6062E1-9710-4E5A-B3F8-8923BF7CC60F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6230FA33-5ABD-45A1-A34C-1A4C0ACE019D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8680F1B5-7AC4-4CC4-B915-17BE4AE62367}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6B4128-7D74-4EC5-81D5-CFF20E5DB199}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E65F867-192D-4F2F-BF45-F37F8F7308D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F6062E1-9710-4E5A-B3F8-8923BF7CC60F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C11D04D6-B9D5-4E64-B326-0AF4A3297C60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8680F1B5-7AC4-4CC4-B915-17BE4AE62367}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28265D83-8C5F-4200-91A3-61978A9A1085}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E65F867-192D-4F2F-BF45-F37F8F7308D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA48884-0D7E-46B7-A690-C63255A3C60E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C11D04D6-B9D5-4E64-B326-0AF4A3297C60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD6E092-B794-4B0A-9D6A-B595690BC208}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28265D83-8C5F-4200-91A3-61978A9A1085}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D74A5072-A74B-46BD-9B99-2A3AB9EADCB2}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA48884-0D7E-46B7-A690-C63255A3C60E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90FBDC9A-AB02-4080-B91C-200FB61B5847}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD6E092-B794-4B0A-9D6A-B595690BC208}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{729C184C-12E4-4FDA-9D3A-735A066BE61F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D74A5072-A74B-46BD-9B99-2A3AB9EADCB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F00F132-0C7A-42CF-BBAB-BCB4C9C653A3}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -11,6 +11,770 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="253">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>Tool_use</t>
+  </si>
+  <si>
+    <t>Extractive_foraging</t>
+  </si>
+  <si>
+    <t>Social_learning</t>
+  </si>
+  <si>
+    <t>Innovation_reduced</t>
+  </si>
+  <si>
+    <t>Tool_use_reduced</t>
+  </si>
+  <si>
+    <t>Extractive_foraging_reduced</t>
+  </si>
+  <si>
+    <t>Journal_search_article_count</t>
+  </si>
+  <si>
+    <t>Zoological_record_article_count</t>
+  </si>
+  <si>
+    <t>Ateles belzebuth</t>
+  </si>
+  <si>
+    <t>Ateles chamek</t>
+  </si>
+  <si>
+    <t>Ateles fusciceps</t>
+  </si>
+  <si>
+    <t>Ateles geoffroyi</t>
+  </si>
+  <si>
+    <t>Ateles paniscus</t>
+  </si>
+  <si>
+    <t>Callimico goeldii</t>
+  </si>
+  <si>
+    <t>Callithrix argentata</t>
+  </si>
+  <si>
+    <t>Callithrix aurita</t>
+  </si>
+  <si>
+    <t>Callithrix flaviceps</t>
+  </si>
+  <si>
+    <t>Callithrix geoffroyi</t>
+  </si>
+  <si>
+    <t>Callithrix humeralifer</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Callithrix kuhli</t>
+  </si>
+  <si>
+    <t>Callithrix mauesi</t>
+  </si>
+  <si>
+    <t>Callithrix penicillata</t>
+  </si>
+  <si>
+    <t>Callithrix pygmaea</t>
+  </si>
+  <si>
+    <t>Cebus albifrons</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Cebus apella</t>
+  </si>
+  <si>
+    <t>Cebus capucinus</t>
+  </si>
+  <si>
+    <t>Cebus olivaceus</t>
+  </si>
+  <si>
+    <t>Daubentonia madagascariensis</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Lagothrix flavicauda</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>Lagothrix lagotricha</t>
+  </si>
+  <si>
+    <t>Macaca arctoides</t>
+  </si>
+  <si>
+    <t>Macaca assamensis</t>
+  </si>
+  <si>
+    <t>Macaca cyclopis</t>
+  </si>
+  <si>
+    <t>Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>Macaca fuscata</t>
+  </si>
+  <si>
+    <t>Macaca maura</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Macaca nemestrina</t>
+  </si>
+  <si>
+    <t>Macaca nigra</t>
+  </si>
+  <si>
+    <t>Macaca ochreata</t>
+  </si>
+  <si>
+    <t>Macaca radiata</t>
+  </si>
+  <si>
+    <t>Macaca silenus</t>
+  </si>
+  <si>
+    <t>Macaca sinica</t>
+  </si>
+  <si>
+    <t>Macaca sylvanus</t>
+  </si>
+  <si>
+    <t>Macaca thibetana</t>
+  </si>
+  <si>
+    <t>Macaca tonkeana</t>
+  </si>
+  <si>
+    <t>Miopithecus talapoin</t>
+  </si>
+  <si>
+    <t>Pan paniscus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Papio cynocephalus</t>
+  </si>
+  <si>
+    <t>Papio hamadryas</t>
+  </si>
+  <si>
+    <t>Papio papio</t>
+  </si>
+  <si>
+    <t>Papio ursinus</t>
+  </si>
+  <si>
+    <t>Pongo pygmaeus</t>
+  </si>
+  <si>
+    <t>Saimiri boliviensis</t>
+  </si>
+  <si>
+    <t>Saimiri oerstedii</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Saimiri ustus</t>
+  </si>
+  <si>
+    <t>Saimiri vanzolinii</t>
+  </si>
+  <si>
+    <t>Allenopithecus nigroviridis</t>
+  </si>
+  <si>
+    <t>Allocebus trichotis</t>
+  </si>
+  <si>
+    <t>Alouatta belzebul</t>
+  </si>
+  <si>
+    <t>Alouatta caraya</t>
+  </si>
+  <si>
+    <t>Alouatta coibensis</t>
+  </si>
+  <si>
+    <t>Alouatta fusca</t>
+  </si>
+  <si>
+    <t>Alouatta palliata</t>
+  </si>
+  <si>
+    <t>Alouatta pigra</t>
+  </si>
+  <si>
+    <t>Alouatta sara</t>
+  </si>
+  <si>
+    <t>Alouatta seniculus</t>
+  </si>
+  <si>
+    <t>Aotus azarai</t>
+  </si>
+  <si>
+    <t>Aotus brumbacki</t>
+  </si>
+  <si>
+    <t>Aotus hershkovitzi</t>
+  </si>
+  <si>
+    <t>Aotus infulatus</t>
+  </si>
+  <si>
+    <t>Aotus lemurinus</t>
+  </si>
+  <si>
+    <t>Aotus miconax</t>
+  </si>
+  <si>
+    <t>Aotus nancymaae</t>
+  </si>
+  <si>
+    <t>Aotus nigriceps</t>
+  </si>
+  <si>
+    <t>Aotus trivirgatus</t>
+  </si>
+  <si>
+    <t>Aotus vociferans</t>
+  </si>
+  <si>
+    <t>Arctocebus calabarensis</t>
+  </si>
+  <si>
+    <t>Avahi laniger</t>
+  </si>
+  <si>
+    <t>Avahi occidentalis</t>
+  </si>
+  <si>
+    <t>Brachyteles arachnoides</t>
+  </si>
+  <si>
+    <t>Cacajao calvus</t>
+  </si>
+  <si>
+    <t>Cacajao melanocephalus</t>
+  </si>
+  <si>
+    <t>Cacajao rubicundus</t>
+  </si>
+  <si>
+    <t>Callicebus brunneus</t>
+  </si>
+  <si>
+    <t>Callicebus calligatus</t>
+  </si>
+  <si>
+    <t>Callicebus cinerascens</t>
+  </si>
+  <si>
+    <t>Callicebus cupreus</t>
+  </si>
+  <si>
+    <t>Callicebus donacophilus</t>
+  </si>
+  <si>
+    <t>Callicebus dubius</t>
+  </si>
+  <si>
+    <t>Callicebus hoffmannsi</t>
+  </si>
+  <si>
+    <t>Callicebus modestus</t>
+  </si>
+  <si>
+    <t>Callicebus moloch</t>
+  </si>
+  <si>
+    <t>Callicebus oenanthe</t>
+  </si>
+  <si>
+    <t>Callicebus olallae</t>
+  </si>
+  <si>
+    <t>Callicebus personatus</t>
+  </si>
+  <si>
+    <t>Callicebus torquatus</t>
+  </si>
+  <si>
+    <t>Lophocebus albigena</t>
+  </si>
+  <si>
+    <t>Cercocebus aterrimus</t>
+  </si>
+  <si>
+    <t>Cercocebus galeritus</t>
+  </si>
+  <si>
+    <t>Cercocebus torquatus</t>
+  </si>
+  <si>
+    <t>Chlorocebus aethiops</t>
+  </si>
+  <si>
+    <t>Cercopithecus ascanius</t>
+  </si>
+  <si>
+    <t>Cercopithecus campbelli</t>
+  </si>
+  <si>
+    <t>Cercopithecus cephus</t>
+  </si>
+  <si>
+    <t>Cercopithecus denti</t>
+  </si>
+  <si>
+    <t>Cercopithecus diana</t>
+  </si>
+  <si>
+    <t>Cercopithecus dryas</t>
+  </si>
+  <si>
+    <t>Cercopithecus erythrogaster</t>
+  </si>
+  <si>
+    <t>Cercopithecus erythrotis</t>
+  </si>
+  <si>
+    <t>Cercopithecus hamlyni</t>
+  </si>
+  <si>
+    <t>Cercopithecus lhoesti</t>
+  </si>
+  <si>
+    <t>Cercopithecus mitis</t>
+  </si>
+  <si>
+    <t>Cercopithecus mona</t>
+  </si>
+  <si>
+    <t>Cercopithecus neglectus</t>
+  </si>
+  <si>
+    <t>Cercopithecus nictitans</t>
+  </si>
+  <si>
+    <t>Cercopithecus petaurista</t>
+  </si>
+  <si>
+    <t>Cercopithecus pogonias</t>
+  </si>
+  <si>
+    <t>Cercopithecus preussi</t>
+  </si>
+  <si>
+    <t>Cercopithecus salongo</t>
+  </si>
+  <si>
+    <t>Cercopithecus solatus</t>
+  </si>
+  <si>
+    <t>Cercopithecus wolfi</t>
+  </si>
+  <si>
+    <t>Cheirogaleus major</t>
+  </si>
+  <si>
+    <t>Cheirogaleus medius</t>
+  </si>
+  <si>
+    <t>Chiropotes albinasus</t>
+  </si>
+  <si>
+    <t>Chiropotes satanas</t>
+  </si>
+  <si>
+    <t>Colobus angolensis</t>
+  </si>
+  <si>
+    <t>Piliocolobus badius</t>
+  </si>
+  <si>
+    <t>Procolobus badius</t>
+  </si>
+  <si>
+    <t>Colobus guereza</t>
+  </si>
+  <si>
+    <t>Procolobus kirkii</t>
+  </si>
+  <si>
+    <t>Colobus polykomos</t>
+  </si>
+  <si>
+    <t>Colobus satanas</t>
+  </si>
+  <si>
+    <t>Erythrocebus patas</t>
+  </si>
+  <si>
+    <t>Euoticus elegantulus</t>
+  </si>
+  <si>
+    <t>Euoticus inustus</t>
+  </si>
+  <si>
+    <t>Galago alleni</t>
+  </si>
+  <si>
+    <t>Galago granti</t>
+  </si>
+  <si>
+    <t>Galago moholi</t>
+  </si>
+  <si>
+    <t>Galago senegalensis</t>
+  </si>
+  <si>
+    <t>Galagoides demidoff</t>
+  </si>
+  <si>
+    <t>Galagoides thomasi</t>
+  </si>
+  <si>
+    <t>Galagoides zanzibaricus</t>
+  </si>
+  <si>
+    <t>Hapalemur aureus</t>
+  </si>
+  <si>
+    <t>Hapalemur griseus</t>
+  </si>
+  <si>
+    <t>Hapalemur simus</t>
+  </si>
+  <si>
+    <t>Hylobates agilis</t>
+  </si>
+  <si>
+    <t>Hylobates concolor</t>
+  </si>
+  <si>
+    <t>Hylobates gabriellae</t>
+  </si>
+  <si>
+    <t>Hylobates hoolock</t>
+  </si>
+  <si>
+    <t>Hylobates klossii</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Hylobates leucogenys</t>
+  </si>
+  <si>
+    <t>Hylobates moloch</t>
+  </si>
+  <si>
+    <t>Hylobates muelleri</t>
+  </si>
+  <si>
+    <t>Hylobates pileatus</t>
+  </si>
+  <si>
+    <t>Symphalangus syndactylus</t>
+  </si>
+  <si>
+    <t>Hylobates syndactylus</t>
+  </si>
+  <si>
+    <t>Indri indri</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Leontopithecus chrysomelas</t>
+  </si>
+  <si>
+    <t>Leontopithecus chrysopygus</t>
+  </si>
+  <si>
+    <t>Leontopithecus rosalia</t>
+  </si>
+  <si>
+    <t>Lepilemur dorsalis</t>
+  </si>
+  <si>
+    <t>Lepilemur edwardsi</t>
+  </si>
+  <si>
+    <t>Lepilemur leucopus</t>
+  </si>
+  <si>
+    <t>Lepilemur microdon</t>
+  </si>
+  <si>
+    <t>Lepilemur mustelinus</t>
+  </si>
+  <si>
+    <t>Lepilemur ruficaudatus</t>
+  </si>
+  <si>
+    <t>Lepilemur septentrionalis</t>
+  </si>
+  <si>
+    <t>Loris tardigradus</t>
+  </si>
+  <si>
+    <t>Mandrillus leucophaeus</t>
+  </si>
+  <si>
+    <t>Mandrillus sphinx</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Microcebus myoxinus</t>
+  </si>
+  <si>
+    <t>Microcebus ravelobensis</t>
+  </si>
+  <si>
+    <t>Microcebus rufus</t>
+  </si>
+  <si>
+    <t>Microcebus coquereli</t>
+  </si>
+  <si>
+    <t>Nasalis larvatus</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Nycticebus pygmaeus</t>
+  </si>
+  <si>
+    <t>Otolemur crassicaudatus</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Perodicticus potto</t>
+  </si>
+  <si>
+    <t>Eulemur coronatus</t>
+  </si>
+  <si>
+    <t>Eulemur fulvus</t>
+  </si>
+  <si>
+    <t>Eulemur macaco</t>
+  </si>
+  <si>
+    <t>Eulemur mongoz</t>
+  </si>
+  <si>
+    <t>Eulemur rubriventer</t>
+  </si>
+  <si>
+    <t>Phaner furcifer</t>
+  </si>
+  <si>
+    <t>Pithecia aequatorialis</t>
+  </si>
+  <si>
+    <t>Pithecia albicans</t>
+  </si>
+  <si>
+    <t>Pithecia irrorata</t>
+  </si>
+  <si>
+    <t>Pithecia monachus</t>
+  </si>
+  <si>
+    <t>Pithecia pithecia</t>
+  </si>
+  <si>
+    <t>Trachypithecus auratus</t>
+  </si>
+  <si>
+    <t>Presbytis comata</t>
+  </si>
+  <si>
+    <t>Trachypithecus cristatus</t>
+  </si>
+  <si>
+    <t>Trachypithecus delacouri</t>
+  </si>
+  <si>
+    <t>Semnopithecus entellus</t>
+  </si>
+  <si>
+    <t>Trachypithecus francoisi</t>
+  </si>
+  <si>
+    <t>Presbytis frontata</t>
+  </si>
+  <si>
+    <t>Presbytis geei</t>
+  </si>
+  <si>
+    <t>Trachypithecus johnii</t>
+  </si>
+  <si>
+    <t>Presbytis melalophos</t>
+  </si>
+  <si>
+    <t>Trachypithecus obscurus</t>
+  </si>
+  <si>
+    <t>Trachypithecus phayrei</t>
+  </si>
+  <si>
+    <t>Trachypithecus pileatus</t>
+  </si>
+  <si>
+    <t>Presbytis potenziani</t>
+  </si>
+  <si>
+    <t>Presbytis rubicunda</t>
+  </si>
+  <si>
+    <t>Presbytis thomasi</t>
+  </si>
+  <si>
+    <t>Presbytis vetulus</t>
+  </si>
+  <si>
+    <t>Procolobus pennantii</t>
+  </si>
+  <si>
+    <t>Procolobus preussi</t>
+  </si>
+  <si>
+    <t>Procolobus verus</t>
+  </si>
+  <si>
+    <t>Propithecus diadema</t>
+  </si>
+  <si>
+    <t>Propithecus tattersalli</t>
+  </si>
+  <si>
+    <t>Propithecus verreauxi</t>
+  </si>
+  <si>
+    <t>Pygathrix avunculus</t>
+  </si>
+  <si>
+    <t>Pygathrix bieti</t>
+  </si>
+  <si>
+    <t>Pygathrix brelichi</t>
+  </si>
+  <si>
+    <t>Pygathrix nemaeus</t>
+  </si>
+  <si>
+    <t>Pygathrix roxellana</t>
+  </si>
+  <si>
+    <t>Saguinus bicolor</t>
+  </si>
+  <si>
+    <t>Saguinus fuscicollis</t>
+  </si>
+  <si>
+    <t>Saguinus geoffroyi</t>
+  </si>
+  <si>
+    <t>Saguinus imperator</t>
+  </si>
+  <si>
+    <t>Saguinus inustus</t>
+  </si>
+  <si>
+    <t>Saguinus labiatus</t>
+  </si>
+  <si>
+    <t>Saguinus leucopus</t>
+  </si>
+  <si>
+    <t>Saguinus midas</t>
+  </si>
+  <si>
+    <t>Saguinus mystax</t>
+  </si>
+  <si>
+    <t>Saguinus nigricollis</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Saguinus tripartitus</t>
+  </si>
+  <si>
+    <t>Nasalis concolor</t>
+  </si>
+  <si>
+    <t>Tarsius bancanus</t>
+  </si>
+  <si>
+    <t>Tarsius dianae</t>
+  </si>
+  <si>
+    <t>Tarsius pumilis</t>
+  </si>
+  <si>
+    <t>Tarsius spectrum</t>
+  </si>
+  <si>
+    <t>Tarsius syrichta</t>
+  </si>
+  <si>
+    <t>Theropithecus gelada</t>
+  </si>
+  <si>
+    <t>Varecia variegata</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,73 +1118,47 @@
   <dimension ref="A1:K239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Innovation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tool_use</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Extractive_foraging</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Social_learning</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Innovation_reduced</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Tool_use_reduced</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Extractive_foraging_reduced</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Journal_search_article_count</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Zoological_record_article_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ateles belzebuth</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ateles belzebuth</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -450,16 +1188,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ateles chamek</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ateles chamek</t>
-        </is>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -486,16 +1220,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -525,16 +1255,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -564,16 +1290,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ateles paniscus</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ateles paniscus</t>
-        </is>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -603,16 +1325,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Callimico goeldii</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Callimico goeldii</t>
-        </is>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -642,16 +1360,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Callithrix argentata</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Callithrix argentata</t>
-        </is>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -681,16 +1395,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Callithrix aurita</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Callithrix aurita</t>
-        </is>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -717,16 +1427,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Callithrix flaviceps</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Callithrix flaviceps</t>
-        </is>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -753,16 +1459,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Callithrix geoffroyi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Callithrix geoffroyi</t>
-        </is>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -789,16 +1491,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Callithrix humeralifer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Callithrix humeralifer</t>
-        </is>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -825,16 +1523,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -864,16 +1558,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Callithrix kuhli</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Callithrix kuhli</t>
-        </is>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -900,16 +1590,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Callithrix mauesi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Callithrix mauesi</t>
-        </is>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -936,16 +1622,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Callithrix penicillata</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Callithrix penicillata</t>
-        </is>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -972,16 +1654,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Callithrix pygmaea</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Callithrix pygmaea</t>
-        </is>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1011,16 +1689,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cebus albifrons</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cebus albifrons</t>
-        </is>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1050,16 +1724,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cebus apella</t>
-        </is>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
       </c>
       <c r="C19">
         <v>39</v>
@@ -1089,16 +1759,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Cebus capucinus</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cebus capucinus</t>
-        </is>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -1128,16 +1794,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cebus olivaceus</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cebus olivaceus</t>
-        </is>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1167,16 +1829,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascariensis</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascariensis</t>
-        </is>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1206,16 +1864,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
       </c>
       <c r="C23">
         <v>25</v>
@@ -1245,16 +1899,12 @@
         <v>517</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Lagothrix flavicauda</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Lagothrix flavicauda</t>
-        </is>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1281,16 +1931,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Lagothrix lagotricha</t>
-        </is>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1320,16 +1966,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Macaca arctoides</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Macaca arctoides</t>
-        </is>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1359,16 +2001,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Macaca assamensis</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Macaca assamensis</t>
-        </is>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1398,16 +2036,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Macaca cyclopis</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Macaca cyclopis</t>
-        </is>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1437,16 +2071,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -1476,16 +2106,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Macaca fuscata</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Macaca fuscata</t>
-        </is>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -1515,16 +2141,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Macaca maura</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Macaca maura</t>
-        </is>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1554,16 +2176,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -1593,16 +2211,12 @@
         <v>296</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1632,16 +2246,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Macaca nigra</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Macaca nigra</t>
-        </is>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1671,16 +2281,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Macaca ochreata</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Macaca ochreata</t>
-        </is>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1710,16 +2316,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Macaca radiata</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Macaca radiata</t>
-        </is>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1749,16 +2351,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1788,16 +2386,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Macaca sinica</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Macaca sinica</t>
-        </is>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1827,16 +2421,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1866,16 +2456,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Macaca thibetana</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Macaca thibetana</t>
-        </is>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1905,16 +2491,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1944,16 +2526,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1983,16 +2561,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
       </c>
       <c r="C43">
         <v>10</v>
@@ -2022,16 +2596,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
       </c>
       <c r="C44">
         <v>321</v>
@@ -2061,16 +2631,12 @@
         <v>755</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
       </c>
       <c r="C45">
         <v>12</v>
@@ -2100,16 +2666,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Papio cynocephalus</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Papio cynocephalus</t>
-        </is>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2139,16 +2701,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Papio hamadryas</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Papio hamadryas</t>
-        </is>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
       </c>
       <c r="C47">
         <v>6</v>
@@ -2178,16 +2736,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Papio papio</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Papio papio</t>
-        </is>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
       </c>
       <c r="C48">
         <v>8</v>
@@ -2217,16 +2771,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Papio ursinus</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Papio ursinus</t>
-        </is>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -2256,16 +2806,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
       </c>
       <c r="C50">
         <v>53</v>
@@ -2295,16 +2841,12 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Saimiri boliviensis</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Saimiri boliviensis</t>
-        </is>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2334,16 +2876,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Saimiri oerstedii</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Saimiri oerstedii</t>
-        </is>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
+        <v>63</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2373,16 +2911,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -2412,16 +2946,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Saimiri ustus</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Saimiri ustus</t>
-        </is>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" t="s">
+        <v>65</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2448,16 +2978,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Saimiri vanzolinii</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Saimiri vanzolinii</t>
-        </is>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" t="s">
+        <v>66</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2484,16 +3010,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Allenopithecus nigroviridis</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Allenopithecus nigroviridis</t>
-        </is>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2520,16 +3042,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Allocebus trichotis</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Allocebus trichotis</t>
-        </is>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2559,16 +3077,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Alouatta belzebul</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Alouatta belzebul</t>
-        </is>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>69</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2598,16 +3112,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Alouatta caraya</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Alouatta caraya</t>
-        </is>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" t="s">
+        <v>70</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2637,16 +3147,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Alouatta coibensis</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Alouatta coibensis</t>
-        </is>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" t="s">
+        <v>71</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2673,16 +3179,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Alouatta fusca</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Alouatta fusca</t>
-        </is>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" t="s">
+        <v>72</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -2712,16 +3214,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Alouatta palliata</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Alouatta palliata</t>
-        </is>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2751,16 +3249,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Alouatta pigra</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Alouatta pigra</t>
-        </is>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2790,16 +3284,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Alouatta sara</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Alouatta sara</t>
-        </is>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>75</v>
+      </c>
+      <c r="B64" t="s">
+        <v>75</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2826,16 +3316,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Alouatta seniculus</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Alouatta seniculus</t>
-        </is>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" t="s">
+        <v>76</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -2865,16 +3351,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Aotus azarai</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Aotus azarai</t>
-        </is>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" t="s">
+        <v>77</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2904,16 +3386,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Aotus brumbacki</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Aotus brumbacki</t>
-        </is>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" t="s">
+        <v>78</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2940,16 +3418,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Aotus hershkovitzi</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Aotus hershkovitzi</t>
-        </is>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" t="s">
+        <v>79</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2976,16 +3450,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Aotus infulatus</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Aotus infulatus</t>
-        </is>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" t="s">
+        <v>80</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3012,16 +3482,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Aotus lemurinus</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Aotus lemurinus</t>
-        </is>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" t="s">
+        <v>81</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3051,16 +3517,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Aotus miconax</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Aotus miconax</t>
-        </is>
+    <row r="71" spans="1:11">
+      <c r="A71" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" t="s">
+        <v>82</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3087,16 +3549,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Aotus nancymaae</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Aotus nancymaae</t>
-        </is>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" t="s">
+        <v>83</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3126,16 +3584,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Aotus nigriceps</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Aotus nigriceps</t>
-        </is>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" t="s">
+        <v>84</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3162,16 +3616,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
+    <row r="74" spans="1:11">
+      <c r="A74" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" t="s">
+        <v>85</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3201,16 +3651,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Aotus vociferans</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Aotus vociferans</t>
-        </is>
+    <row r="75" spans="1:11">
+      <c r="A75" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" t="s">
+        <v>86</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3240,16 +3686,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Arctocebus calabarensis</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Arctocebus calabarensis</t>
-        </is>
+    <row r="76" spans="1:11">
+      <c r="A76" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" t="s">
+        <v>87</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3276,16 +3718,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Avahi laniger</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Avahi laniger</t>
-        </is>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" t="s">
+        <v>88</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3312,16 +3750,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Avahi occidentalis</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Avahi occidentalis</t>
-        </is>
+    <row r="78" spans="1:11">
+      <c r="A78" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" t="s">
+        <v>89</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3348,16 +3782,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Brachyteles arachnoides</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Brachyteles arachnoides</t>
-        </is>
+    <row r="79" spans="1:11">
+      <c r="A79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79" t="s">
+        <v>90</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3387,16 +3817,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Cacajao calvus</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Cacajao calvus</t>
-        </is>
+    <row r="80" spans="1:11">
+      <c r="A80" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3423,16 +3849,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Cacajao melanocephalus</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Cacajao melanocephalus</t>
-        </is>
+    <row r="81" spans="1:11">
+      <c r="A81" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" t="s">
+        <v>92</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3462,16 +3884,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Cacajao rubicundus</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Cacajao rubicundus</t>
-        </is>
+    <row r="82" spans="1:11">
+      <c r="A82" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" t="s">
+        <v>93</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3501,16 +3919,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Callicebus brunneus</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Callicebus brunneus</t>
-        </is>
+    <row r="83" spans="1:11">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" t="s">
+        <v>94</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3537,16 +3951,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Callicebus calligatus</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Callicebus calligatus</t>
-        </is>
+    <row r="84" spans="1:11">
+      <c r="A84" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" t="s">
+        <v>95</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3573,16 +3983,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Callicebus cinerascens</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Callicebus cinerascens</t>
-        </is>
+    <row r="85" spans="1:11">
+      <c r="A85" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85" t="s">
+        <v>96</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3609,16 +4015,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Callicebus cupreus</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Callicebus cupreus</t>
-        </is>
+    <row r="86" spans="1:11">
+      <c r="A86" t="s">
+        <v>97</v>
+      </c>
+      <c r="B86" t="s">
+        <v>97</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3648,16 +4050,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Callicebus donacophilus</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Callicebus donacophilus</t>
-        </is>
+    <row r="87" spans="1:11">
+      <c r="A87" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87" t="s">
+        <v>98</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3684,16 +4082,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Callicebus dubius</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Callicebus dubius</t>
-        </is>
+    <row r="88" spans="1:11">
+      <c r="A88" t="s">
+        <v>99</v>
+      </c>
+      <c r="B88" t="s">
+        <v>99</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3720,16 +4114,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Callicebus hoffmannsi</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Callicebus hoffmannsi</t>
-        </is>
+    <row r="89" spans="1:11">
+      <c r="A89" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89" t="s">
+        <v>100</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -3756,16 +4146,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Callicebus modestus</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Callicebus modestus</t>
-        </is>
+    <row r="90" spans="1:11">
+      <c r="A90" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" t="s">
+        <v>101</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3792,16 +4178,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Callicebus moloch</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Callicebus moloch</t>
-        </is>
+    <row r="91" spans="1:11">
+      <c r="A91" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" t="s">
+        <v>102</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3831,16 +4213,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Callicebus oenanthe</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Callicebus oenanthe</t>
-        </is>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" t="s">
+        <v>103</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3867,16 +4245,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Callicebus olallae</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Callicebus olallae</t>
-        </is>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>104</v>
+      </c>
+      <c r="B93" t="s">
+        <v>104</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -3903,16 +4277,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Callicebus personatus</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Callicebus personatus</t>
-        </is>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>105</v>
+      </c>
+      <c r="B94" t="s">
+        <v>105</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3942,16 +4312,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Callicebus torquatus</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Callicebus torquatus</t>
-        </is>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>106</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3981,16 +4347,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Lophocebus albigena</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Lophocebus albigena</t>
-        </is>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>107</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4020,16 +4382,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cercocebus aterrimus</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Cercocebus aterrimus</t>
-        </is>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>108</v>
+      </c>
+      <c r="B97" t="s">
+        <v>108</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4056,16 +4414,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Cercocebus galeritus</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Cercocebus galeritus</t>
-        </is>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>109</v>
+      </c>
+      <c r="B98" t="s">
+        <v>109</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4095,16 +4449,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>110</v>
+      </c>
+      <c r="B99" t="s">
+        <v>110</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4134,16 +4484,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Chlorocebus aethiops</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Chlorocebus aethiops</t>
-        </is>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>111</v>
+      </c>
+      <c r="B100" t="s">
+        <v>111</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -4173,16 +4519,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>112</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4212,16 +4554,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Cercopithecus campbelli</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Cercopithecus campbelli</t>
-        </is>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>113</v>
+      </c>
+      <c r="B102" t="s">
+        <v>113</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4248,16 +4586,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Cercopithecus cephus</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Cercopithecus cephus</t>
-        </is>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103" t="s">
+        <v>114</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4284,16 +4618,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Cercopithecus denti</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Cercopithecus denti</t>
-        </is>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>115</v>
+      </c>
+      <c r="B104" t="s">
+        <v>115</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -4320,16 +4650,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>116</v>
+      </c>
+      <c r="B105" t="s">
+        <v>116</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4359,16 +4685,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Cercopithecus dryas</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Cercopithecus dryas</t>
-        </is>
+    <row r="106" spans="1:11">
+      <c r="A106" t="s">
+        <v>117</v>
+      </c>
+      <c r="B106" t="s">
+        <v>117</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4395,16 +4717,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Cercopithecus erythrogaster</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Cercopithecus erythrogaster</t>
-        </is>
+    <row r="107" spans="1:11">
+      <c r="A107" t="s">
+        <v>118</v>
+      </c>
+      <c r="B107" t="s">
+        <v>118</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4431,16 +4749,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Cercopithecus erythrotis</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Cercopithecus erythrotis</t>
-        </is>
+    <row r="108" spans="1:11">
+      <c r="A108" t="s">
+        <v>119</v>
+      </c>
+      <c r="B108" t="s">
+        <v>119</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4467,16 +4781,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Cercopithecus hamlyni</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Cercopithecus hamlyni</t>
-        </is>
+    <row r="109" spans="1:11">
+      <c r="A109" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109" t="s">
+        <v>120</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4503,16 +4813,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Cercopithecus lhoesti</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Cercopithecus lhoesti</t>
-        </is>
+    <row r="110" spans="1:11">
+      <c r="A110" t="s">
+        <v>121</v>
+      </c>
+      <c r="B110" t="s">
+        <v>121</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -4542,16 +4848,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Cercopithecus mitis</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Cercopithecus mitis</t>
-        </is>
+    <row r="111" spans="1:11">
+      <c r="A111" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111" t="s">
+        <v>122</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -4581,16 +4883,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cercopithecus mona</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Cercopithecus mona</t>
-        </is>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
+        <v>123</v>
+      </c>
+      <c r="B112" t="s">
+        <v>123</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -4620,16 +4918,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Cercopithecus neglectus</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Cercopithecus neglectus</t>
-        </is>
+    <row r="113" spans="1:11">
+      <c r="A113" t="s">
+        <v>124</v>
+      </c>
+      <c r="B113" t="s">
+        <v>124</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4659,16 +4953,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Cercopithecus nictitans</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Cercopithecus nictitans</t>
-        </is>
+    <row r="114" spans="1:11">
+      <c r="A114" t="s">
+        <v>125</v>
+      </c>
+      <c r="B114" t="s">
+        <v>125</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4695,16 +4985,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Cercopithecus petaurista</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Cercopithecus petaurista</t>
-        </is>
+    <row r="115" spans="1:11">
+      <c r="A115" t="s">
+        <v>126</v>
+      </c>
+      <c r="B115" t="s">
+        <v>126</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -4731,16 +5017,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Cercopithecus pogonias</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Cercopithecus pogonias</t>
-        </is>
+    <row r="116" spans="1:11">
+      <c r="A116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" t="s">
+        <v>127</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -4770,16 +5052,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Cercopithecus preussi</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Cercopithecus preussi</t>
-        </is>
+    <row r="117" spans="1:11">
+      <c r="A117" t="s">
+        <v>128</v>
+      </c>
+      <c r="B117" t="s">
+        <v>128</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -4806,16 +5084,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Cercopithecus salongo</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Cercopithecus salongo</t>
-        </is>
+    <row r="118" spans="1:11">
+      <c r="A118" t="s">
+        <v>129</v>
+      </c>
+      <c r="B118" t="s">
+        <v>129</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -4842,16 +5116,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Cercopithecus solatus</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Cercopithecus solatus</t>
-        </is>
+    <row r="119" spans="1:11">
+      <c r="A119" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119" t="s">
+        <v>130</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4881,16 +5151,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Cercopithecus wolfi</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Cercopithecus wolfi</t>
-        </is>
+    <row r="120" spans="1:11">
+      <c r="A120" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120" t="s">
+        <v>131</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -4917,16 +5183,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Cheirogaleus major</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Cheirogaleus major</t>
-        </is>
+    <row r="121" spans="1:11">
+      <c r="A121" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -4953,16 +5215,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Cheirogaleus medius</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Cheirogaleus medius</t>
-        </is>
+    <row r="122" spans="1:11">
+      <c r="A122" t="s">
+        <v>133</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -4992,16 +5250,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Chiropotes albinasus</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Chiropotes albinasus</t>
-        </is>
+    <row r="123" spans="1:11">
+      <c r="A123" t="s">
+        <v>134</v>
+      </c>
+      <c r="B123" t="s">
+        <v>134</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -5031,16 +5285,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Chiropotes satanas</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Chiropotes satanas</t>
-        </is>
+    <row r="124" spans="1:11">
+      <c r="A124" t="s">
+        <v>135</v>
+      </c>
+      <c r="B124" t="s">
+        <v>135</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -5070,16 +5320,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Colobus angolensis</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Colobus angolensis</t>
-        </is>
+    <row r="125" spans="1:11">
+      <c r="A125" t="s">
+        <v>136</v>
+      </c>
+      <c r="B125" t="s">
+        <v>136</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -5109,16 +5355,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Piliocolobus badius</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Procolobus badius</t>
-        </is>
+    <row r="126" spans="1:11">
+      <c r="A126" t="s">
+        <v>137</v>
+      </c>
+      <c r="B126" t="s">
+        <v>138</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5148,16 +5390,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Colobus guereza</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Colobus guereza</t>
-        </is>
+    <row r="127" spans="1:11">
+      <c r="A127" t="s">
+        <v>139</v>
+      </c>
+      <c r="B127" t="s">
+        <v>139</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -5187,16 +5425,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Procolobus kirkii</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Procolobus kirkii</t>
-        </is>
+    <row r="128" spans="1:11">
+      <c r="A128" t="s">
+        <v>140</v>
+      </c>
+      <c r="B128" t="s">
+        <v>140</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -5226,16 +5460,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Colobus polykomos</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Colobus polykomos</t>
-        </is>
+    <row r="129" spans="1:11">
+      <c r="A129" t="s">
+        <v>141</v>
+      </c>
+      <c r="B129" t="s">
+        <v>141</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -5265,16 +5495,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Colobus satanas</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Colobus satanas</t>
-        </is>
+    <row r="130" spans="1:11">
+      <c r="A130" t="s">
+        <v>142</v>
+      </c>
+      <c r="B130" t="s">
+        <v>142</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -5304,16 +5530,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Erythrocebus patas</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Erythrocebus patas</t>
-        </is>
+    <row r="131" spans="1:11">
+      <c r="A131" t="s">
+        <v>143</v>
+      </c>
+      <c r="B131" t="s">
+        <v>143</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5343,16 +5565,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Euoticus elegantulus</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Euoticus elegantulus</t>
-        </is>
+    <row r="132" spans="1:11">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+      <c r="B132" t="s">
+        <v>144</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5382,16 +5600,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Euoticus inustus</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Euoticus inustus</t>
-        </is>
+    <row r="133" spans="1:11">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+      <c r="B133" t="s">
+        <v>145</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -5418,16 +5632,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Galago alleni</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Galago alleni</t>
-        </is>
+    <row r="134" spans="1:11">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+      <c r="B134" t="s">
+        <v>146</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -5457,16 +5667,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Galago granti</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Galago granti</t>
-        </is>
+    <row r="135" spans="1:11">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+      <c r="B135" t="s">
+        <v>147</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -5493,16 +5699,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Galago moholi</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Galago moholi</t>
-        </is>
+    <row r="136" spans="1:11">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+      <c r="B136" t="s">
+        <v>148</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5532,16 +5734,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
+    <row r="137" spans="1:11">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+      <c r="B137" t="s">
+        <v>149</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -5571,16 +5769,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
+    <row r="138" spans="1:11">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+      <c r="B138" t="s">
+        <v>150</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5610,16 +5804,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Galagoides thomasi</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Galagoides thomasi</t>
-        </is>
+    <row r="139" spans="1:11">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+      <c r="B139" t="s">
+        <v>151</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -5646,16 +5836,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Galagoides zanzibaricus</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Galagoides zanzibaricus</t>
-        </is>
+    <row r="140" spans="1:11">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+      <c r="B140" t="s">
+        <v>152</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5682,16 +5868,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Hapalemur aureus</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Hapalemur aureus</t>
-        </is>
+    <row r="141" spans="1:11">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+      <c r="B141" t="s">
+        <v>153</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5718,16 +5900,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Hapalemur griseus</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Hapalemur griseus</t>
-        </is>
+    <row r="142" spans="1:11">
+      <c r="A142" t="s">
+        <v>154</v>
+      </c>
+      <c r="B142" t="s">
+        <v>154</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -5757,16 +5935,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Hapalemur simus</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Hapalemur simus</t>
-        </is>
+    <row r="143" spans="1:11">
+      <c r="A143" t="s">
+        <v>155</v>
+      </c>
+      <c r="B143" t="s">
+        <v>155</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -5796,16 +5970,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Hylobates agilis</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Hylobates agilis</t>
-        </is>
+    <row r="144" spans="1:11">
+      <c r="A144" t="s">
+        <v>156</v>
+      </c>
+      <c r="B144" t="s">
+        <v>156</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -5835,16 +6005,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Hylobates concolor</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Hylobates concolor</t>
-        </is>
+    <row r="145" spans="1:11">
+      <c r="A145" t="s">
+        <v>157</v>
+      </c>
+      <c r="B145" t="s">
+        <v>157</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -5874,16 +6040,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Hylobates gabriellae</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Hylobates gabriellae</t>
-        </is>
+    <row r="146" spans="1:11">
+      <c r="A146" t="s">
+        <v>158</v>
+      </c>
+      <c r="B146" t="s">
+        <v>158</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5913,16 +6075,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Hylobates hoolock</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Hylobates hoolock</t>
-        </is>
+    <row r="147" spans="1:11">
+      <c r="A147" t="s">
+        <v>159</v>
+      </c>
+      <c r="B147" t="s">
+        <v>159</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -5952,16 +6110,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Hylobates klossii</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Hylobates klossii</t>
-        </is>
+    <row r="148" spans="1:11">
+      <c r="A148" t="s">
+        <v>160</v>
+      </c>
+      <c r="B148" t="s">
+        <v>160</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -5991,16 +6145,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
+    <row r="149" spans="1:11">
+      <c r="A149" t="s">
+        <v>161</v>
+      </c>
+      <c r="B149" t="s">
+        <v>161</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -6030,16 +6180,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Hylobates leucogenys</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Hylobates leucogenys</t>
-        </is>
+    <row r="150" spans="1:11">
+      <c r="A150" t="s">
+        <v>162</v>
+      </c>
+      <c r="B150" t="s">
+        <v>162</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -6069,16 +6215,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
+    <row r="151" spans="1:11">
+      <c r="A151" t="s">
+        <v>163</v>
+      </c>
+      <c r="B151" t="s">
+        <v>163</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6105,16 +6247,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Hylobates muelleri</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Hylobates muelleri</t>
-        </is>
+    <row r="152" spans="1:11">
+      <c r="A152" t="s">
+        <v>164</v>
+      </c>
+      <c r="B152" t="s">
+        <v>164</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6144,16 +6282,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Hylobates pileatus</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Hylobates pileatus</t>
-        </is>
+    <row r="153" spans="1:11">
+      <c r="A153" t="s">
+        <v>165</v>
+      </c>
+      <c r="B153" t="s">
+        <v>165</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -6183,16 +6317,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Hylobates syndactylus</t>
-        </is>
+    <row r="154" spans="1:11">
+      <c r="A154" t="s">
+        <v>166</v>
+      </c>
+      <c r="B154" t="s">
+        <v>167</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6222,16 +6352,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Indri indri</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Indri indri</t>
-        </is>
+    <row r="155" spans="1:11">
+      <c r="A155" t="s">
+        <v>168</v>
+      </c>
+      <c r="B155" t="s">
+        <v>168</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6261,16 +6387,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+    <row r="156" spans="1:11">
+      <c r="A156" t="s">
+        <v>169</v>
+      </c>
+      <c r="B156" t="s">
+        <v>169</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -6300,16 +6422,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysomelas</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysomelas</t>
-        </is>
+    <row r="157" spans="1:11">
+      <c r="A157" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" t="s">
+        <v>170</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -6339,16 +6457,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysopygus</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Leontopithecus chrysopygus</t>
-        </is>
+    <row r="158" spans="1:11">
+      <c r="A158" t="s">
+        <v>171</v>
+      </c>
+      <c r="B158" t="s">
+        <v>171</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6378,16 +6492,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
+    <row r="159" spans="1:11">
+      <c r="A159" t="s">
+        <v>172</v>
+      </c>
+      <c r="B159" t="s">
+        <v>172</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -6417,16 +6527,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Lepilemur dorsalis</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Lepilemur dorsalis</t>
-        </is>
+    <row r="160" spans="1:11">
+      <c r="A160" t="s">
+        <v>173</v>
+      </c>
+      <c r="B160" t="s">
+        <v>173</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -6456,16 +6562,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Lepilemur edwardsi</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Lepilemur edwardsi</t>
-        </is>
+    <row r="161" spans="1:11">
+      <c r="A161" t="s">
+        <v>174</v>
+      </c>
+      <c r="B161" t="s">
+        <v>174</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -6492,16 +6594,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Lepilemur leucopus</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Lepilemur leucopus</t>
-        </is>
+    <row r="162" spans="1:11">
+      <c r="A162" t="s">
+        <v>175</v>
+      </c>
+      <c r="B162" t="s">
+        <v>175</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -6531,16 +6629,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Lepilemur microdon</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Lepilemur microdon</t>
-        </is>
+    <row r="163" spans="1:11">
+      <c r="A163" t="s">
+        <v>176</v>
+      </c>
+      <c r="B163" t="s">
+        <v>176</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -6570,16 +6664,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Lepilemur mustelinus</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Lepilemur mustelinus</t>
-        </is>
+    <row r="164" spans="1:11">
+      <c r="A164" t="s">
+        <v>177</v>
+      </c>
+      <c r="B164" t="s">
+        <v>177</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -6606,16 +6696,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
+    <row r="165" spans="1:11">
+      <c r="A165" t="s">
+        <v>178</v>
+      </c>
+      <c r="B165" t="s">
+        <v>178</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -6645,16 +6731,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Lepilemur septentrionalis</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Lepilemur septentrionalis</t>
-        </is>
+    <row r="166" spans="1:11">
+      <c r="A166" t="s">
+        <v>179</v>
+      </c>
+      <c r="B166" t="s">
+        <v>179</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6681,16 +6763,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Loris tardigradus</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Loris tardigradus</t>
-        </is>
+    <row r="167" spans="1:11">
+      <c r="A167" t="s">
+        <v>180</v>
+      </c>
+      <c r="B167" t="s">
+        <v>180</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6720,16 +6798,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Mandrillus leucophaeus</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Mandrillus leucophaeus</t>
-        </is>
+    <row r="168" spans="1:11">
+      <c r="A168" t="s">
+        <v>181</v>
+      </c>
+      <c r="B168" t="s">
+        <v>181</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -6759,16 +6833,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
+    <row r="169" spans="1:11">
+      <c r="A169" t="s">
+        <v>182</v>
+      </c>
+      <c r="B169" t="s">
+        <v>182</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -6798,16 +6868,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
+    <row r="170" spans="1:11">
+      <c r="A170" t="s">
+        <v>183</v>
+      </c>
+      <c r="B170" t="s">
+        <v>183</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -6837,16 +6903,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Microcebus myoxinus</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Microcebus myoxinus</t>
-        </is>
+    <row r="171" spans="1:11">
+      <c r="A171" t="s">
+        <v>184</v>
+      </c>
+      <c r="B171" t="s">
+        <v>184</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -6873,16 +6935,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Microcebus ravelobensis</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Microcebus ravelobensis</t>
-        </is>
+    <row r="172" spans="1:11">
+      <c r="A172" t="s">
+        <v>185</v>
+      </c>
+      <c r="B172" t="s">
+        <v>185</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -6909,16 +6967,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Microcebus rufus</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Microcebus rufus</t>
-        </is>
+    <row r="173" spans="1:11">
+      <c r="A173" t="s">
+        <v>186</v>
+      </c>
+      <c r="B173" t="s">
+        <v>186</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -6948,16 +7002,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Microcebus coquereli</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Microcebus coquereli</t>
-        </is>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>187</v>
+      </c>
+      <c r="B174" t="s">
+        <v>187</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -6987,16 +7037,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Nasalis larvatus</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Nasalis larvatus</t>
-        </is>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>188</v>
+      </c>
+      <c r="B175" t="s">
+        <v>188</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -7026,16 +7072,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>189</v>
+      </c>
+      <c r="B176" t="s">
+        <v>189</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -7065,16 +7107,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Nycticebus pygmaeus</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Nycticebus pygmaeus</t>
-        </is>
+    <row r="177" spans="1:11">
+      <c r="A177" t="s">
+        <v>190</v>
+      </c>
+      <c r="B177" t="s">
+        <v>190</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -7104,16 +7142,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Otolemur crassicaudatus</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Otolemur crassicaudatus</t>
-        </is>
+    <row r="178" spans="1:11">
+      <c r="A178" t="s">
+        <v>191</v>
+      </c>
+      <c r="B178" t="s">
+        <v>191</v>
       </c>
       <c r="C178">
         <v>2</v>
@@ -7143,16 +7177,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
+    <row r="179" spans="1:11">
+      <c r="A179" t="s">
+        <v>192</v>
+      </c>
+      <c r="B179" t="s">
+        <v>192</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7182,16 +7212,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
+    <row r="180" spans="1:11">
+      <c r="A180" t="s">
+        <v>193</v>
+      </c>
+      <c r="B180" t="s">
+        <v>193</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -7221,16 +7247,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
+    <row r="181" spans="1:11">
+      <c r="A181" t="s">
+        <v>194</v>
+      </c>
+      <c r="B181" t="s">
+        <v>194</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -7260,16 +7282,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
+    <row r="182" spans="1:11">
+      <c r="A182" t="s">
+        <v>195</v>
+      </c>
+      <c r="B182" t="s">
+        <v>195</v>
       </c>
       <c r="C182">
         <v>3</v>
@@ -7299,16 +7317,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
+    <row r="183" spans="1:11">
+      <c r="A183" t="s">
+        <v>196</v>
+      </c>
+      <c r="B183" t="s">
+        <v>196</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7338,16 +7352,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
+    <row r="184" spans="1:11">
+      <c r="A184" t="s">
+        <v>197</v>
+      </c>
+      <c r="B184" t="s">
+        <v>197</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -7377,16 +7387,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Eulemur rubriventer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Eulemur rubriventer</t>
-        </is>
+    <row r="185" spans="1:11">
+      <c r="A185" t="s">
+        <v>198</v>
+      </c>
+      <c r="B185" t="s">
+        <v>198</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -7416,16 +7422,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Phaner furcifer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Phaner furcifer</t>
-        </is>
+    <row r="186" spans="1:11">
+      <c r="A186" t="s">
+        <v>199</v>
+      </c>
+      <c r="B186" t="s">
+        <v>199</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7455,16 +7457,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Pithecia aequatorialis</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Pithecia aequatorialis</t>
-        </is>
+    <row r="187" spans="1:11">
+      <c r="A187" t="s">
+        <v>200</v>
+      </c>
+      <c r="B187" t="s">
+        <v>200</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -7491,16 +7489,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Pithecia albicans</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Pithecia albicans</t>
-        </is>
+    <row r="188" spans="1:11">
+      <c r="A188" t="s">
+        <v>201</v>
+      </c>
+      <c r="B188" t="s">
+        <v>201</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -7530,16 +7524,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Pithecia irrorata</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Pithecia irrorata</t>
-        </is>
+    <row r="189" spans="1:11">
+      <c r="A189" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" t="s">
+        <v>202</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -7569,16 +7559,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Pithecia monachus</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Pithecia monachus</t>
-        </is>
+    <row r="190" spans="1:11">
+      <c r="A190" t="s">
+        <v>203</v>
+      </c>
+      <c r="B190" t="s">
+        <v>203</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -7605,16 +7591,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
+    <row r="191" spans="1:11">
+      <c r="A191" t="s">
+        <v>204</v>
+      </c>
+      <c r="B191" t="s">
+        <v>204</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7644,16 +7626,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
+    <row r="192" spans="1:11">
+      <c r="A192" t="s">
+        <v>205</v>
+      </c>
+      <c r="B192" t="s">
+        <v>205</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -7683,16 +7661,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Presbytis comata</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Presbytis comata</t>
-        </is>
+    <row r="193" spans="1:11">
+      <c r="A193" t="s">
+        <v>206</v>
+      </c>
+      <c r="B193" t="s">
+        <v>206</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -7719,16 +7693,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Trachypithecus cristatus</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Trachypithecus cristatus</t>
-        </is>
+    <row r="194" spans="1:11">
+      <c r="A194" t="s">
+        <v>207</v>
+      </c>
+      <c r="B194" t="s">
+        <v>207</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -7758,16 +7728,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Trachypithecus delacouri</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Trachypithecus delacouri</t>
-        </is>
+    <row r="195" spans="1:11">
+      <c r="A195" t="s">
+        <v>208</v>
+      </c>
+      <c r="B195" t="s">
+        <v>208</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -7794,16 +7760,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
+    <row r="196" spans="1:11">
+      <c r="A196" t="s">
+        <v>209</v>
+      </c>
+      <c r="B196" t="s">
+        <v>209</v>
       </c>
       <c r="C196">
         <v>7</v>
@@ -7833,16 +7795,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Trachypithecus francoisi</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Trachypithecus francoisi</t>
-        </is>
+    <row r="197" spans="1:11">
+      <c r="A197" t="s">
+        <v>210</v>
+      </c>
+      <c r="B197" t="s">
+        <v>210</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -7872,16 +7830,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Presbytis frontata</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Presbytis frontata</t>
-        </is>
+    <row r="198" spans="1:11">
+      <c r="A198" t="s">
+        <v>211</v>
+      </c>
+      <c r="B198" t="s">
+        <v>211</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -7908,16 +7862,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Presbytis geei</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Presbytis geei</t>
-        </is>
+    <row r="199" spans="1:11">
+      <c r="A199" t="s">
+        <v>212</v>
+      </c>
+      <c r="B199" t="s">
+        <v>212</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -7944,16 +7894,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Trachypithecus johnii</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Trachypithecus johnii</t>
-        </is>
+    <row r="200" spans="1:11">
+      <c r="A200" t="s">
+        <v>213</v>
+      </c>
+      <c r="B200" t="s">
+        <v>213</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -7983,16 +7929,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Presbytis melalophos</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Presbytis melalophos</t>
-        </is>
+    <row r="201" spans="1:11">
+      <c r="A201" t="s">
+        <v>214</v>
+      </c>
+      <c r="B201" t="s">
+        <v>214</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -8022,16 +7964,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Trachypithecus obscurus</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Trachypithecus obscurus</t>
-        </is>
+    <row r="202" spans="1:11">
+      <c r="A202" t="s">
+        <v>215</v>
+      </c>
+      <c r="B202" t="s">
+        <v>215</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -8061,16 +7999,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Trachypithecus phayrei</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Trachypithecus phayrei</t>
-        </is>
+    <row r="203" spans="1:11">
+      <c r="A203" t="s">
+        <v>216</v>
+      </c>
+      <c r="B203" t="s">
+        <v>216</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -8100,16 +8034,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Trachypithecus pileatus</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Trachypithecus pileatus</t>
-        </is>
+    <row r="204" spans="1:11">
+      <c r="A204" t="s">
+        <v>217</v>
+      </c>
+      <c r="B204" t="s">
+        <v>217</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -8139,16 +8069,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Presbytis potenziani</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Presbytis potenziani</t>
-        </is>
+    <row r="205" spans="1:11">
+      <c r="A205" t="s">
+        <v>218</v>
+      </c>
+      <c r="B205" t="s">
+        <v>218</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -8175,16 +8101,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Presbytis rubicunda</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Presbytis rubicunda</t>
-        </is>
+    <row r="206" spans="1:11">
+      <c r="A206" t="s">
+        <v>219</v>
+      </c>
+      <c r="B206" t="s">
+        <v>219</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -8214,16 +8136,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Presbytis thomasi</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Presbytis thomasi</t>
-        </is>
+    <row r="207" spans="1:11">
+      <c r="A207" t="s">
+        <v>220</v>
+      </c>
+      <c r="B207" t="s">
+        <v>220</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -8250,16 +8168,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Presbytis vetulus</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Presbytis vetulus</t>
-        </is>
+    <row r="208" spans="1:11">
+      <c r="A208" t="s">
+        <v>221</v>
+      </c>
+      <c r="B208" t="s">
+        <v>221</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -8286,16 +8200,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Procolobus pennantii</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Procolobus pennantii</t>
-        </is>
+    <row r="209" spans="1:11">
+      <c r="A209" t="s">
+        <v>222</v>
+      </c>
+      <c r="B209" t="s">
+        <v>222</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -8322,16 +8232,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Procolobus preussi</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Procolobus preussi</t>
-        </is>
+    <row r="210" spans="1:11">
+      <c r="A210" t="s">
+        <v>223</v>
+      </c>
+      <c r="B210" t="s">
+        <v>223</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -8358,16 +8264,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Procolobus verus</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Procolobus verus</t>
-        </is>
+    <row r="211" spans="1:11">
+      <c r="A211" t="s">
+        <v>224</v>
+      </c>
+      <c r="B211" t="s">
+        <v>224</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -8394,16 +8296,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Propithecus diadema</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Propithecus diadema</t>
-        </is>
+    <row r="212" spans="1:11">
+      <c r="A212" t="s">
+        <v>225</v>
+      </c>
+      <c r="B212" t="s">
+        <v>225</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -8433,16 +8331,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Propithecus tattersalli</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Propithecus tattersalli</t>
-        </is>
+    <row r="213" spans="1:11">
+      <c r="A213" t="s">
+        <v>226</v>
+      </c>
+      <c r="B213" t="s">
+        <v>226</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -8472,16 +8366,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
+    <row r="214" spans="1:11">
+      <c r="A214" t="s">
+        <v>227</v>
+      </c>
+      <c r="B214" t="s">
+        <v>227</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -8511,16 +8401,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Pygathrix avunculus</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Pygathrix avunculus</t>
-        </is>
+    <row r="215" spans="1:11">
+      <c r="A215" t="s">
+        <v>228</v>
+      </c>
+      <c r="B215" t="s">
+        <v>228</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -8550,16 +8436,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Pygathrix bieti</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Pygathrix bieti</t>
-        </is>
+    <row r="216" spans="1:11">
+      <c r="A216" t="s">
+        <v>229</v>
+      </c>
+      <c r="B216" t="s">
+        <v>229</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8586,16 +8468,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Pygathrix brelichi</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Pygathrix brelichi</t>
-        </is>
+    <row r="217" spans="1:11">
+      <c r="A217" t="s">
+        <v>230</v>
+      </c>
+      <c r="B217" t="s">
+        <v>230</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -8625,16 +8503,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Pygathrix nemaeus</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Pygathrix nemaeus</t>
-        </is>
+    <row r="218" spans="1:11">
+      <c r="A218" t="s">
+        <v>231</v>
+      </c>
+      <c r="B218" t="s">
+        <v>231</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -8664,16 +8538,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Pygathrix roxellana</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Pygathrix roxellana</t>
-        </is>
+    <row r="219" spans="1:11">
+      <c r="A219" t="s">
+        <v>232</v>
+      </c>
+      <c r="B219" t="s">
+        <v>232</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8703,16 +8573,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Saguinus bicolor</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Saguinus bicolor</t>
-        </is>
+    <row r="220" spans="1:11">
+      <c r="A220" t="s">
+        <v>233</v>
+      </c>
+      <c r="B220" t="s">
+        <v>233</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -8742,16 +8608,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Saguinus fuscicollis</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Saguinus fuscicollis</t>
-        </is>
+    <row r="221" spans="1:11">
+      <c r="A221" t="s">
+        <v>234</v>
+      </c>
+      <c r="B221" t="s">
+        <v>234</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8781,16 +8643,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Saguinus geoffroyi</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Saguinus geoffroyi</t>
-        </is>
+    <row r="222" spans="1:11">
+      <c r="A222" t="s">
+        <v>235</v>
+      </c>
+      <c r="B222" t="s">
+        <v>235</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -8817,16 +8675,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Saguinus imperator</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Saguinus imperator</t>
-        </is>
+    <row r="223" spans="1:11">
+      <c r="A223" t="s">
+        <v>236</v>
+      </c>
+      <c r="B223" t="s">
+        <v>236</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -8856,16 +8710,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Saguinus inustus</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Saguinus inustus</t>
-        </is>
+    <row r="224" spans="1:11">
+      <c r="A224" t="s">
+        <v>237</v>
+      </c>
+      <c r="B224" t="s">
+        <v>237</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -8892,16 +8742,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Saguinus labiatus</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Saguinus labiatus</t>
-        </is>
+    <row r="225" spans="1:11">
+      <c r="A225" t="s">
+        <v>238</v>
+      </c>
+      <c r="B225" t="s">
+        <v>238</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -8931,16 +8777,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Saguinus leucopus</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Saguinus leucopus</t>
-        </is>
+    <row r="226" spans="1:11">
+      <c r="A226" t="s">
+        <v>239</v>
+      </c>
+      <c r="B226" t="s">
+        <v>239</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8967,16 +8809,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
+    <row r="227" spans="1:11">
+      <c r="A227" t="s">
+        <v>240</v>
+      </c>
+      <c r="B227" t="s">
+        <v>240</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -9006,16 +8844,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Saguinus mystax</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Saguinus mystax</t>
-        </is>
+    <row r="228" spans="1:11">
+      <c r="A228" t="s">
+        <v>241</v>
+      </c>
+      <c r="B228" t="s">
+        <v>241</v>
       </c>
       <c r="C228">
         <v>4</v>
@@ -9045,16 +8879,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Saguinus nigricollis</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Saguinus nigricollis</t>
-        </is>
+    <row r="229" spans="1:11">
+      <c r="A229" t="s">
+        <v>242</v>
+      </c>
+      <c r="B229" t="s">
+        <v>242</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -9084,16 +8914,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
+    <row r="230" spans="1:11">
+      <c r="A230" t="s">
+        <v>243</v>
+      </c>
+      <c r="B230" t="s">
+        <v>243</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -9123,16 +8949,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Saguinus tripartitus</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Saguinus tripartitus</t>
-        </is>
+    <row r="231" spans="1:11">
+      <c r="A231" t="s">
+        <v>244</v>
+      </c>
+      <c r="B231" t="s">
+        <v>244</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -9162,16 +8984,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Nasalis concolor</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Nasalis concolor</t>
-        </is>
+    <row r="232" spans="1:11">
+      <c r="A232" t="s">
+        <v>245</v>
+      </c>
+      <c r="B232" t="s">
+        <v>245</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -9201,16 +9019,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Tarsius bancanus</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Tarsius bancanus</t>
-        </is>
+    <row r="233" spans="1:11">
+      <c r="A233" t="s">
+        <v>246</v>
+      </c>
+      <c r="B233" t="s">
+        <v>246</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -9240,16 +9054,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Tarsius dianae</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Tarsius dianae</t>
-        </is>
+    <row r="234" spans="1:11">
+      <c r="A234" t="s">
+        <v>247</v>
+      </c>
+      <c r="B234" t="s">
+        <v>247</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -9279,16 +9089,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Tarsius pumilis</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Tarsius pumilis</t>
-        </is>
+    <row r="235" spans="1:11">
+      <c r="A235" t="s">
+        <v>248</v>
+      </c>
+      <c r="B235" t="s">
+        <v>248</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -9315,16 +9121,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Tarsius spectrum</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Tarsius spectrum</t>
-        </is>
+    <row r="236" spans="1:11">
+      <c r="A236" t="s">
+        <v>249</v>
+      </c>
+      <c r="B236" t="s">
+        <v>249</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -9354,16 +9156,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Tarsius syrichta</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Tarsius syrichta</t>
-        </is>
+    <row r="237" spans="1:11">
+      <c r="A237" t="s">
+        <v>250</v>
+      </c>
+      <c r="B237" t="s">
+        <v>250</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9390,16 +9188,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
+    <row r="238" spans="1:11">
+      <c r="A238" t="s">
+        <v>251</v>
+      </c>
+      <c r="B238" t="s">
+        <v>251</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9429,16 +9223,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
+    <row r="239" spans="1:11">
+      <c r="A239" t="s">
+        <v>252</v>
+      </c>
+      <c r="B239" t="s">
+        <v>252</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -9749,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90FBDC9A-AB02-4080-B91C-200FB61B5847}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF6FC4C9-E089-4EE2-8AD0-4B9A175AD7B8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{729C184C-12E4-4FDA-9D3A-735A066BE61F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27092981-0ECB-40B1-B42C-B6F542D50379}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F00F132-0C7A-42CF-BBAB-BCB4C9C653A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E834FEE-CC0C-44B0-838A-0EA61D0A097D}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF6FC4C9-E089-4EE2-8AD0-4B9A175AD7B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C75C6-118B-4492-BF55-A8047BC8A9A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27092981-0ECB-40B1-B42C-B6F542D50379}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E1D344-DEFE-4EE1-8AAD-9B9D96CC0EFD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E834FEE-CC0C-44B0-838A-0EA61D0A097D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D049D41-831D-4ACB-9CCC-9E89791CB099}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C75C6-118B-4492-BF55-A8047BC8A9A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26FFFD4C-2B78-4B00-9854-46C15DE6E0C6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E1D344-DEFE-4EE1-8AAD-9B9D96CC0EFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDE122BE-D768-48D1-AA99-75102D6173FA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D049D41-831D-4ACB-9CCC-9E89791CB099}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEED952-2F9F-4A9A-8D1C-C29A5DE28D30}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,291 +9261,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26FFFD4C-2B78-4B00-9854-46C15DE6E0C6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDE122BE-D768-48D1-AA99-75102D6173FA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEED952-2F9F-4A9A-8D1C-C29A5DE28D30}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,4 +9261,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99B5BD52-58BB-41FD-8677-D289418DEC5E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43EAE657-B199-4931-8684-2884B190FAEC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C9EAC6-4CAE-41CC-BEA9-CD56C91A0ADE}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,291 +9261,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99B5BD52-58BB-41FD-8677-D289418DEC5E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43EAE657-B199-4931-8684-2884B190FAEC}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C9EAC6-4CAE-41CC-BEA9-CD56C91A0ADE}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,4 +9261,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D7043CA-6D4D-45E9-A89D-E420467A2C34}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDAB88-2FEB-4E2C-B6FF-7D2A7F610490}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC105921-1994-444E-9883-AE5194FE2E3C}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D7043CA-6D4D-45E9-A89D-E420467A2C34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89D8DC56-1CE5-435F-99B8-C4EE60A95216}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDAB88-2FEB-4E2C-B6FF-7D2A7F610490}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF9C61F7-7E17-4AB3-86F2-3689188DA2F6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC105921-1994-444E-9883-AE5194FE2E3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00B02C7F-78FA-4A65-B2C9-C7FF1137EFD5}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89D8DC56-1CE5-435F-99B8-C4EE60A95216}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8926C3B1-F80C-46E0-AB8D-DE7737270AF8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF9C61F7-7E17-4AB3-86F2-3689188DA2F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1497A4BE-4FA4-46A4-82B6-138FFBF181D6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00B02C7F-78FA-4A65-B2C9-C7FF1137EFD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17D0945-8248-4518-BC83-226FBE96EEDB}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8926C3B1-F80C-46E0-AB8D-DE7737270AF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3767B75-B9AC-4D01-B380-CAE0A5FCC3B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1497A4BE-4FA4-46A4-82B6-138FFBF181D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A393D6D-1FC9-4A67-B61F-5DBC967D69C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17D0945-8248-4518-BC83-226FBE96EEDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{493E5546-501B-43AC-8A4E-92ED41662434}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3767B75-B9AC-4D01-B380-CAE0A5FCC3B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7394C58-E828-48BA-A95E-479862648252}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A393D6D-1FC9-4A67-B61F-5DBC967D69C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F5A3114-F35F-4908-8E12-38ECDC643603}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{493E5546-501B-43AC-8A4E-92ED41662434}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D60E53B-689A-4C99-88F4-7E5D4D70F73B}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7394C58-E828-48BA-A95E-479862648252}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8CB076-5906-4757-AD0B-A1F65C038355}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F5A3114-F35F-4908-8E12-38ECDC643603}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A11ADBE-A9BF-456E-89BB-4C36F75FDEC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D60E53B-689A-4C99-88F4-7E5D4D70F73B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EA9C11-6CC5-41E5-B78C-62344C76A9B4}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,291 +9261,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8CB076-5906-4757-AD0B-A1F65C038355}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A11ADBE-A9BF-456E-89BB-4C36F75FDEC8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EA9C11-6CC5-41E5-B78C-62344C76A9B4}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,4 +9261,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{603A3DD6-7A2C-4452-B36B-C8AFA40BF1F0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D7C3F7A-2E00-4228-B3D9-C569E4572F2B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC94277D-B16B-41F9-9691-8B553E2D2384}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="249">
   <si>
     <t>species_sci</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Cebus albifrons</t>
   </si>
   <si>
-    <t>Sapajus apella</t>
-  </si>
-  <si>
     <t>Cebus apella</t>
   </si>
   <si>
@@ -121,9 +118,6 @@
     <t>Lagothrix flavicauda</t>
   </si>
   <si>
-    <t>Lagothrix lagothricha</t>
-  </si>
-  <si>
     <t>Lagothrix lagotricha</t>
   </si>
   <si>
@@ -427,9 +421,6 @@
     <t>Colobus angolensis</t>
   </si>
   <si>
-    <t>Piliocolobus badius</t>
-  </si>
-  <si>
     <t>Procolobus badius</t>
   </si>
   <si>
@@ -512,9 +503,6 @@
   </si>
   <si>
     <t>Hylobates pileatus</t>
-  </si>
-  <si>
-    <t>Symphalangus syndactylus</t>
   </si>
   <si>
     <t>Hylobates syndactylus</t>
@@ -1729,7 +1717,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>39</v>
@@ -1761,10 +1749,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -1796,10 +1784,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1831,10 +1819,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1866,10 +1854,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>25</v>
@@ -1901,10 +1889,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1933,10 +1921,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1968,10 +1956,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2003,10 +1991,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2038,10 +2026,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2073,10 +2061,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2108,10 +2096,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -2143,10 +2131,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2178,10 +2166,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -2213,10 +2201,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2248,10 +2236,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2283,10 +2271,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2318,10 +2306,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -2353,10 +2341,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2388,10 +2376,10 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2423,10 +2411,10 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2458,10 +2446,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2493,10 +2481,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2528,10 +2516,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2563,10 +2551,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>10</v>
@@ -2598,10 +2586,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>321</v>
@@ -2633,10 +2621,10 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>12</v>
@@ -2668,10 +2656,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2703,10 +2691,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>6</v>
@@ -2738,10 +2726,10 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>8</v>
@@ -2773,10 +2761,10 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -2808,10 +2796,10 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>53</v>
@@ -2843,10 +2831,10 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2878,10 +2866,10 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2913,10 +2901,10 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -2948,10 +2936,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2980,10 +2968,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -3012,10 +3000,10 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -3044,10 +3032,10 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3079,10 +3067,10 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3114,10 +3102,10 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3149,10 +3137,10 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3181,10 +3169,10 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3216,10 +3204,10 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3251,10 +3239,10 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3286,10 +3274,10 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3318,10 +3306,10 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -3353,10 +3341,10 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3388,10 +3376,10 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3420,10 +3408,10 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3452,10 +3440,10 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3484,10 +3472,10 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3519,10 +3507,10 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3551,10 +3539,10 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3586,10 +3574,10 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3618,10 +3606,10 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3653,10 +3641,10 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3688,10 +3676,10 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3720,10 +3708,10 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3752,10 +3740,10 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3784,10 +3772,10 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3819,10 +3807,10 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3851,10 +3839,10 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3886,10 +3874,10 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3921,10 +3909,10 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3953,10 +3941,10 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3985,10 +3973,10 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4017,10 +4005,10 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4052,10 +4040,10 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4084,10 +4072,10 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -4116,10 +4104,10 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4148,10 +4136,10 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4180,10 +4168,10 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4215,10 +4203,10 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4247,10 +4235,10 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4279,10 +4267,10 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4314,10 +4302,10 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -4349,10 +4337,10 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4384,10 +4372,10 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4416,10 +4404,10 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4451,10 +4439,10 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4486,10 +4474,10 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -4521,10 +4509,10 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4556,10 +4544,10 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4588,10 +4576,10 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4620,10 +4608,10 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -4652,10 +4640,10 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4687,10 +4675,10 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4719,10 +4707,10 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4751,10 +4739,10 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B108" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4783,10 +4771,10 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4815,10 +4803,10 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -4850,10 +4838,10 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -4885,10 +4873,10 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -4920,10 +4908,10 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4955,10 +4943,10 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B114" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4987,10 +4975,10 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B115" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5019,10 +5007,10 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5054,10 +5042,10 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -5086,10 +5074,10 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B118" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -5118,10 +5106,10 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B119" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5153,10 +5141,10 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B120" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -5185,10 +5173,10 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5217,10 +5205,10 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -5252,10 +5240,10 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -5287,10 +5275,10 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B124" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -5322,10 +5310,10 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -5357,10 +5345,10 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5392,10 +5380,10 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -5427,10 +5415,10 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -5462,10 +5450,10 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B129" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -5497,10 +5485,10 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B130" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -5532,10 +5520,10 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B131" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5567,10 +5555,10 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B132" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5602,10 +5590,10 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B133" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -5634,10 +5622,10 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B134" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -5669,10 +5657,10 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -5701,10 +5689,10 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B136" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5736,10 +5724,10 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B137" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -5771,10 +5759,10 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B138" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5806,10 +5794,10 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B139" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -5838,10 +5826,10 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5870,10 +5858,10 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5902,10 +5890,10 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B142" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -5937,10 +5925,10 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B143" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -5972,10 +5960,10 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -6007,10 +5995,10 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B145" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -6042,10 +6030,10 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -6077,10 +6065,10 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B147" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -6112,10 +6100,10 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -6147,10 +6135,10 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -6182,10 +6170,10 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B150" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -6217,10 +6205,10 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B151" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6249,10 +6237,10 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B152" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6284,10 +6272,10 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B153" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -6319,10 +6307,10 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6354,10 +6342,10 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B155" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6389,10 +6377,10 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B156" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -6424,10 +6412,10 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B157" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -6459,10 +6447,10 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B158" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6494,10 +6482,10 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B159" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -6529,10 +6517,10 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -6564,10 +6552,10 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B161" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -6596,10 +6584,10 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B162" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -6631,10 +6619,10 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B163" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -6666,10 +6654,10 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B164" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -6698,10 +6686,10 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B165" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -6733,10 +6721,10 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B166" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6765,10 +6753,10 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B167" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6800,10 +6788,10 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B168" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -6835,10 +6823,10 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B169" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -6870,10 +6858,10 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B170" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -6905,10 +6893,10 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B171" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -6937,10 +6925,10 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B172" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -6969,10 +6957,10 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B173" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -7004,10 +6992,10 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -7039,10 +7027,10 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B175" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -7074,10 +7062,10 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B176" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -7109,10 +7097,10 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B177" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -7144,10 +7132,10 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B178" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C178">
         <v>2</v>
@@ -7179,10 +7167,10 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B179" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7214,10 +7202,10 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B180" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -7249,10 +7237,10 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B181" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -7284,10 +7272,10 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B182" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C182">
         <v>3</v>
@@ -7319,10 +7307,10 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B183" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7354,10 +7342,10 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B184" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -7389,10 +7377,10 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B185" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -7424,10 +7412,10 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B186" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7459,10 +7447,10 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B187" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -7491,10 +7479,10 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B188" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -7526,10 +7514,10 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -7561,10 +7549,10 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B190" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -7593,10 +7581,10 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B191" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7628,10 +7616,10 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B192" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -7663,10 +7651,10 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B193" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -7695,10 +7683,10 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B194" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -7730,10 +7718,10 @@
     </row>
     <row r="195" spans="1:11">
       <c r="A195" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B195" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -7762,10 +7750,10 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B196" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C196">
         <v>7</v>
@@ -7797,10 +7785,10 @@
     </row>
     <row r="197" spans="1:11">
       <c r="A197" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B197" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -7832,10 +7820,10 @@
     </row>
     <row r="198" spans="1:11">
       <c r="A198" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B198" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -7864,10 +7852,10 @@
     </row>
     <row r="199" spans="1:11">
       <c r="A199" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B199" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -7896,10 +7884,10 @@
     </row>
     <row r="200" spans="1:11">
       <c r="A200" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B200" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -7931,10 +7919,10 @@
     </row>
     <row r="201" spans="1:11">
       <c r="A201" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B201" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -7966,10 +7954,10 @@
     </row>
     <row r="202" spans="1:11">
       <c r="A202" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B202" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -8001,10 +7989,10 @@
     </row>
     <row r="203" spans="1:11">
       <c r="A203" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B203" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -8036,10 +8024,10 @@
     </row>
     <row r="204" spans="1:11">
       <c r="A204" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B204" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -8071,10 +8059,10 @@
     </row>
     <row r="205" spans="1:11">
       <c r="A205" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B205" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -8103,10 +8091,10 @@
     </row>
     <row r="206" spans="1:11">
       <c r="A206" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B206" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -8138,10 +8126,10 @@
     </row>
     <row r="207" spans="1:11">
       <c r="A207" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B207" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -8170,10 +8158,10 @@
     </row>
     <row r="208" spans="1:11">
       <c r="A208" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B208" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -8202,10 +8190,10 @@
     </row>
     <row r="209" spans="1:11">
       <c r="A209" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B209" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -8234,10 +8222,10 @@
     </row>
     <row r="210" spans="1:11">
       <c r="A210" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B210" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -8266,10 +8254,10 @@
     </row>
     <row r="211" spans="1:11">
       <c r="A211" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B211" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -8298,10 +8286,10 @@
     </row>
     <row r="212" spans="1:11">
       <c r="A212" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B212" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -8333,10 +8321,10 @@
     </row>
     <row r="213" spans="1:11">
       <c r="A213" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B213" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -8368,10 +8356,10 @@
     </row>
     <row r="214" spans="1:11">
       <c r="A214" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B214" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -8403,10 +8391,10 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B215" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -8438,10 +8426,10 @@
     </row>
     <row r="216" spans="1:11">
       <c r="A216" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B216" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8470,10 +8458,10 @@
     </row>
     <row r="217" spans="1:11">
       <c r="A217" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B217" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -8505,10 +8493,10 @@
     </row>
     <row r="218" spans="1:11">
       <c r="A218" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B218" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -8540,10 +8528,10 @@
     </row>
     <row r="219" spans="1:11">
       <c r="A219" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B219" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8575,10 +8563,10 @@
     </row>
     <row r="220" spans="1:11">
       <c r="A220" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B220" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -8610,10 +8598,10 @@
     </row>
     <row r="221" spans="1:11">
       <c r="A221" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B221" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8645,10 +8633,10 @@
     </row>
     <row r="222" spans="1:11">
       <c r="A222" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B222" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -8677,10 +8665,10 @@
     </row>
     <row r="223" spans="1:11">
       <c r="A223" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B223" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -8712,10 +8700,10 @@
     </row>
     <row r="224" spans="1:11">
       <c r="A224" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -8744,10 +8732,10 @@
     </row>
     <row r="225" spans="1:11">
       <c r="A225" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B225" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -8779,10 +8767,10 @@
     </row>
     <row r="226" spans="1:11">
       <c r="A226" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B226" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8811,10 +8799,10 @@
     </row>
     <row r="227" spans="1:11">
       <c r="A227" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B227" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -8846,10 +8834,10 @@
     </row>
     <row r="228" spans="1:11">
       <c r="A228" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B228" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C228">
         <v>4</v>
@@ -8881,10 +8869,10 @@
     </row>
     <row r="229" spans="1:11">
       <c r="A229" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B229" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -8916,10 +8904,10 @@
     </row>
     <row r="230" spans="1:11">
       <c r="A230" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B230" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -8951,10 +8939,10 @@
     </row>
     <row r="231" spans="1:11">
       <c r="A231" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B231" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -8986,10 +8974,10 @@
     </row>
     <row r="232" spans="1:11">
       <c r="A232" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B232" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -9021,10 +9009,10 @@
     </row>
     <row r="233" spans="1:11">
       <c r="A233" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B233" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -9056,10 +9044,10 @@
     </row>
     <row r="234" spans="1:11">
       <c r="A234" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B234" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -9091,10 +9079,10 @@
     </row>
     <row r="235" spans="1:11">
       <c r="A235" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B235" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -9123,10 +9111,10 @@
     </row>
     <row r="236" spans="1:11">
       <c r="A236" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B236" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -9158,10 +9146,10 @@
     </row>
     <row r="237" spans="1:11">
       <c r="A237" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B237" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9190,10 +9178,10 @@
     </row>
     <row r="238" spans="1:11">
       <c r="A238" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B238" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9225,10 +9213,10 @@
     </row>
     <row r="239" spans="1:11">
       <c r="A239" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B239" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -9539,13 +9527,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{603A3DD6-7A2C-4452-B36B-C8AFA40BF1F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{182B562D-5D73-4D86-B515-5F288F1B0DFF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D7C3F7A-2E00-4228-B3D9-C569E4572F2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{249A8E00-F035-4866-A609-DBB9064547C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC94277D-B16B-41F9-9691-8B553E2D2384}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D92A085A-128A-4182-9E05-A1320A44A1E3}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9527,13 +9527,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{182B562D-5D73-4D86-B515-5F288F1B0DFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6D9C349-48D9-4241-B34F-7E09455D1F2D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{249A8E00-F035-4866-A609-DBB9064547C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02926C04-D2F6-4484-92E4-94F29054BE18}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D92A085A-128A-4182-9E05-A1320A44A1E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{493C2401-5469-4378-BE59-E8B724391C7C}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="253">
   <si>
     <t>species_sci</t>
   </si>
@@ -100,6 +100,9 @@
     <t>Cebus albifrons</t>
   </si>
   <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
     <t>Cebus apella</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>Lagothrix flavicauda</t>
   </si>
   <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
     <t>Lagothrix lagotricha</t>
   </si>
   <si>
@@ -421,6 +427,9 @@
     <t>Colobus angolensis</t>
   </si>
   <si>
+    <t>Piliocolobus badius</t>
+  </si>
+  <si>
     <t>Procolobus badius</t>
   </si>
   <si>
@@ -503,6 +512,9 @@
   </si>
   <si>
     <t>Hylobates pileatus</t>
+  </si>
+  <si>
+    <t>Symphalangus syndactylus</t>
   </si>
   <si>
     <t>Hylobates syndactylus</t>
@@ -1717,7 +1729,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>39</v>
@@ -1749,10 +1761,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -1784,10 +1796,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1819,10 +1831,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1854,10 +1866,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23">
         <v>25</v>
@@ -1889,10 +1901,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1921,10 +1933,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1956,10 +1968,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1991,10 +2003,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2026,10 +2038,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2061,10 +2073,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2096,10 +2108,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -2131,10 +2143,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2166,10 +2178,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -2201,10 +2213,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2236,10 +2248,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2271,10 +2283,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2306,10 +2318,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -2341,10 +2353,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2376,10 +2388,10 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2411,10 +2423,10 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2446,10 +2458,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2481,10 +2493,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2516,10 +2528,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2551,10 +2563,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C43">
         <v>10</v>
@@ -2586,10 +2598,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C44">
         <v>321</v>
@@ -2621,10 +2633,10 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C45">
         <v>12</v>
@@ -2656,10 +2668,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2691,10 +2703,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C47">
         <v>6</v>
@@ -2726,10 +2738,10 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C48">
         <v>8</v>
@@ -2761,10 +2773,10 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -2796,10 +2808,10 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C50">
         <v>53</v>
@@ -2831,10 +2843,10 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2866,10 +2878,10 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2901,10 +2913,10 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -2936,10 +2948,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2968,10 +2980,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -3000,10 +3012,10 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -3032,10 +3044,10 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3067,10 +3079,10 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3102,10 +3114,10 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3137,10 +3149,10 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3169,10 +3181,10 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3204,10 +3216,10 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3239,10 +3251,10 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3274,10 +3286,10 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3306,10 +3318,10 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -3341,10 +3353,10 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3376,10 +3388,10 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3408,10 +3420,10 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B68" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3440,10 +3452,10 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3472,10 +3484,10 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3507,10 +3519,10 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3539,10 +3551,10 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3574,10 +3586,10 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3606,10 +3618,10 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3641,10 +3653,10 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3676,10 +3688,10 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3708,10 +3720,10 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3740,10 +3752,10 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3772,10 +3784,10 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3807,10 +3819,10 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3839,10 +3851,10 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3874,10 +3886,10 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3909,10 +3921,10 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3941,10 +3953,10 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3973,10 +3985,10 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4005,10 +4017,10 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4040,10 +4052,10 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4072,10 +4084,10 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -4104,10 +4116,10 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4136,10 +4148,10 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4168,10 +4180,10 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4203,10 +4215,10 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4235,10 +4247,10 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4267,10 +4279,10 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B94" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4302,10 +4314,10 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B95" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -4337,10 +4349,10 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4372,10 +4384,10 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4404,10 +4416,10 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4439,10 +4451,10 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4474,10 +4486,10 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -4509,10 +4521,10 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4544,10 +4556,10 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4576,10 +4588,10 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4608,10 +4620,10 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -4640,10 +4652,10 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4675,10 +4687,10 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4707,10 +4719,10 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4739,10 +4751,10 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4771,10 +4783,10 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4803,10 +4815,10 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -4838,10 +4850,10 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -4873,10 +4885,10 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -4908,10 +4920,10 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4943,10 +4955,10 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4975,10 +4987,10 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5007,10 +5019,10 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5042,10 +5054,10 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -5074,10 +5086,10 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -5106,10 +5118,10 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5141,10 +5153,10 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -5173,10 +5185,10 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5205,10 +5217,10 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -5240,10 +5252,10 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -5275,10 +5287,10 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -5310,10 +5322,10 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -5345,10 +5357,10 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5380,10 +5392,10 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -5415,10 +5427,10 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -5450,10 +5462,10 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -5485,10 +5497,10 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -5520,10 +5532,10 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5555,10 +5567,10 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5590,10 +5602,10 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -5622,10 +5634,10 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -5657,10 +5669,10 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -5689,10 +5701,10 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5724,10 +5736,10 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -5759,10 +5771,10 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5794,10 +5806,10 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B139" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -5826,10 +5838,10 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B140" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5858,10 +5870,10 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B141" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5890,10 +5902,10 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -5925,10 +5937,10 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -5960,10 +5972,10 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -5995,10 +6007,10 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -6030,10 +6042,10 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B146" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -6065,10 +6077,10 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B147" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -6100,10 +6112,10 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B148" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -6135,10 +6147,10 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -6170,10 +6182,10 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -6205,10 +6217,10 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B151" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6237,10 +6249,10 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B152" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6272,10 +6284,10 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -6307,10 +6319,10 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6342,10 +6354,10 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B155" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6377,10 +6389,10 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -6412,10 +6424,10 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B157" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -6447,10 +6459,10 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6482,10 +6494,10 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B159" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -6517,10 +6529,10 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B160" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -6552,10 +6564,10 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B161" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -6584,10 +6596,10 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B162" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -6619,10 +6631,10 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B163" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -6654,10 +6666,10 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B164" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -6686,10 +6698,10 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B165" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -6721,10 +6733,10 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B166" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6753,10 +6765,10 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B167" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6788,10 +6800,10 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B168" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -6823,10 +6835,10 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B169" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -6858,10 +6870,10 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -6893,10 +6905,10 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B171" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -6925,10 +6937,10 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B172" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -6957,10 +6969,10 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B173" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -6992,10 +7004,10 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B174" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -7027,10 +7039,10 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B175" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -7062,10 +7074,10 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B176" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -7097,10 +7109,10 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B177" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -7132,10 +7144,10 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B178" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C178">
         <v>2</v>
@@ -7167,10 +7179,10 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B179" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7202,10 +7214,10 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B180" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -7237,10 +7249,10 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B181" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -7272,10 +7284,10 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B182" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C182">
         <v>3</v>
@@ -7307,10 +7319,10 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B183" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7342,10 +7354,10 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B184" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -7377,10 +7389,10 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B185" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -7412,10 +7424,10 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B186" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7447,10 +7459,10 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B187" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -7479,10 +7491,10 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B188" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -7514,10 +7526,10 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B189" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -7549,10 +7561,10 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B190" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -7581,10 +7593,10 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B191" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7616,10 +7628,10 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B192" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -7651,10 +7663,10 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B193" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -7683,10 +7695,10 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B194" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -7718,10 +7730,10 @@
     </row>
     <row r="195" spans="1:11">
       <c r="A195" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B195" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -7750,10 +7762,10 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B196" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C196">
         <v>7</v>
@@ -7785,10 +7797,10 @@
     </row>
     <row r="197" spans="1:11">
       <c r="A197" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B197" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -7820,10 +7832,10 @@
     </row>
     <row r="198" spans="1:11">
       <c r="A198" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B198" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -7852,10 +7864,10 @@
     </row>
     <row r="199" spans="1:11">
       <c r="A199" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B199" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -7884,10 +7896,10 @@
     </row>
     <row r="200" spans="1:11">
       <c r="A200" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B200" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -7919,10 +7931,10 @@
     </row>
     <row r="201" spans="1:11">
       <c r="A201" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B201" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -7954,10 +7966,10 @@
     </row>
     <row r="202" spans="1:11">
       <c r="A202" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B202" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -7989,10 +8001,10 @@
     </row>
     <row r="203" spans="1:11">
       <c r="A203" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B203" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -8024,10 +8036,10 @@
     </row>
     <row r="204" spans="1:11">
       <c r="A204" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B204" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -8059,10 +8071,10 @@
     </row>
     <row r="205" spans="1:11">
       <c r="A205" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B205" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -8091,10 +8103,10 @@
     </row>
     <row r="206" spans="1:11">
       <c r="A206" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B206" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -8126,10 +8138,10 @@
     </row>
     <row r="207" spans="1:11">
       <c r="A207" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B207" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -8158,10 +8170,10 @@
     </row>
     <row r="208" spans="1:11">
       <c r="A208" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B208" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -8190,10 +8202,10 @@
     </row>
     <row r="209" spans="1:11">
       <c r="A209" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B209" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -8222,10 +8234,10 @@
     </row>
     <row r="210" spans="1:11">
       <c r="A210" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B210" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -8254,10 +8266,10 @@
     </row>
     <row r="211" spans="1:11">
       <c r="A211" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B211" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -8286,10 +8298,10 @@
     </row>
     <row r="212" spans="1:11">
       <c r="A212" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B212" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -8321,10 +8333,10 @@
     </row>
     <row r="213" spans="1:11">
       <c r="A213" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B213" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -8356,10 +8368,10 @@
     </row>
     <row r="214" spans="1:11">
       <c r="A214" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B214" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -8391,10 +8403,10 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B215" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -8426,10 +8438,10 @@
     </row>
     <row r="216" spans="1:11">
       <c r="A216" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B216" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8458,10 +8470,10 @@
     </row>
     <row r="217" spans="1:11">
       <c r="A217" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B217" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -8493,10 +8505,10 @@
     </row>
     <row r="218" spans="1:11">
       <c r="A218" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B218" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -8528,10 +8540,10 @@
     </row>
     <row r="219" spans="1:11">
       <c r="A219" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B219" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8563,10 +8575,10 @@
     </row>
     <row r="220" spans="1:11">
       <c r="A220" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B220" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -8598,10 +8610,10 @@
     </row>
     <row r="221" spans="1:11">
       <c r="A221" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B221" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8633,10 +8645,10 @@
     </row>
     <row r="222" spans="1:11">
       <c r="A222" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B222" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -8665,10 +8677,10 @@
     </row>
     <row r="223" spans="1:11">
       <c r="A223" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B223" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -8700,10 +8712,10 @@
     </row>
     <row r="224" spans="1:11">
       <c r="A224" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B224" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -8732,10 +8744,10 @@
     </row>
     <row r="225" spans="1:11">
       <c r="A225" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B225" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -8767,10 +8779,10 @@
     </row>
     <row r="226" spans="1:11">
       <c r="A226" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B226" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8799,10 +8811,10 @@
     </row>
     <row r="227" spans="1:11">
       <c r="A227" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B227" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -8834,10 +8846,10 @@
     </row>
     <row r="228" spans="1:11">
       <c r="A228" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B228" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C228">
         <v>4</v>
@@ -8869,10 +8881,10 @@
     </row>
     <row r="229" spans="1:11">
       <c r="A229" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B229" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -8904,10 +8916,10 @@
     </row>
     <row r="230" spans="1:11">
       <c r="A230" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B230" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -8939,10 +8951,10 @@
     </row>
     <row r="231" spans="1:11">
       <c r="A231" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B231" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -8974,10 +8986,10 @@
     </row>
     <row r="232" spans="1:11">
       <c r="A232" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B232" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -9009,10 +9021,10 @@
     </row>
     <row r="233" spans="1:11">
       <c r="A233" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B233" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -9044,10 +9056,10 @@
     </row>
     <row r="234" spans="1:11">
       <c r="A234" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B234" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -9079,10 +9091,10 @@
     </row>
     <row r="235" spans="1:11">
       <c r="A235" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B235" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -9111,10 +9123,10 @@
     </row>
     <row r="236" spans="1:11">
       <c r="A236" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B236" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -9146,10 +9158,10 @@
     </row>
     <row r="237" spans="1:11">
       <c r="A237" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B237" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9178,10 +9190,10 @@
     </row>
     <row r="238" spans="1:11">
       <c r="A238" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B238" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9213,10 +9225,10 @@
     </row>
     <row r="239" spans="1:11">
       <c r="A239" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B239" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -9527,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6D9C349-48D9-4241-B34F-7E09455D1F2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D84C81-8889-4470-99B3-E0B71BA44085}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02926C04-D2F6-4484-92E4-94F29054BE18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F483BC9-A3F2-4A94-B293-926CEA6E5DC3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{493C2401-5469-4378-BE59-E8B724391C7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB32A06-F37A-4F51-9301-CE1E679AF158}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D84C81-8889-4470-99B3-E0B71BA44085}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBBE6D7-A7CB-48D8-8967-1816510A076F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F483BC9-A3F2-4A94-B293-926CEA6E5DC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58322A12-573D-4F25-959D-1B2C1945DAA3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB32A06-F37A-4F51-9301-CE1E679AF158}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CED44C-AC02-48CF-8FD5-8FD30F627411}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9539,13 +9539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBBE6D7-A7CB-48D8-8967-1816510A076F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF1C9668-E77D-442E-BD69-979096203E75}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58322A12-573D-4F25-959D-1B2C1945DAA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA037FCC-862C-4BC8-949D-44E6A175CA9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CED44C-AC02-48CF-8FD5-8FD30F627411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23523A86-5D21-4C4A-BA24-0E04DCE22BAE}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,291 +9261,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF1C9668-E77D-442E-BD69-979096203E75}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA037FCC-862C-4BC8-949D-44E6A175CA9C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23523A86-5D21-4C4A-BA24-0E04DCE22BAE}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9261,4 +9261,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CCC6C54-56BA-45FC-9DD9-06C10CBD4777}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A55602-3C76-4156-B64F-6200C02C63A2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E51FA020-0AFB-45B6-A093-858314CFE124}"/>
 </file>